--- a/AAII_Financials/Yearly/WSBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WSBK_YR_FIN.xlsx
@@ -1909,7 +1909,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>685300</v>
+        <v>684000</v>
       </c>
       <c r="E60" s="3">
         <v>641500</v>
@@ -1990,7 +1990,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>147000</v>
+        <v>148200</v>
       </c>
       <c r="E61" s="3">
         <v>129500</v>
